--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F13FE1-B81D-4425-A305-6F7F2D16DFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{44F13FE1-B81D-4425-A305-6F7F2D16DFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8B379D7-100A-41E9-8B50-E94C6C693C56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -78,6 +78,60 @@
   </si>
   <si>
     <t>รูป หลังแก้</t>
+  </si>
+  <si>
+    <t>PhanasonSamutprakhan Residence</t>
+  </si>
+  <si>
+    <t>1ERV-01</t>
+  </si>
+  <si>
+    <t>ปริมาณลมในแบบผู้รับเหมาทำมาไม่ตรงกับรูปอ้างอิง</t>
+  </si>
+  <si>
+    <t>สูง / High</t>
+  </si>
+  <si>
+    <t>กำลังแก้ / In Progress</t>
+  </si>
+  <si>
+    <t>3T</t>
+  </si>
+  <si>
+    <t>S’rin House</t>
+  </si>
+  <si>
+    <t>ห้องกล๊ออฟ</t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง</t>
+  </si>
+  <si>
+    <t>ต่ำ / Low</t>
+  </si>
+  <si>
+    <t>เปิด / รอ</t>
+  </si>
+  <si>
+    <t>บริษัท เคบีเอส ซีสเต็ม จํากัด</t>
+  </si>
+  <si>
+    <t>รอวันที่สามารถเข้าทำงานได้</t>
+  </si>
+  <si>
+    <t>HUAY KWANG RESIDENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รอสรุปหลัง Site meeting </t>
+  </si>
+  <si>
+    <t>Site meeting ก่อนเริ่มงาน 7/24/2026</t>
+  </si>
+  <si>
+    <t>บ้านคุณเต้ย</t>
+  </si>
+  <si>
+    <t>เริ่มงานได้ 3 สิงหา</t>
   </si>
 </sst>
 </file>
@@ -542,7 +596,8 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="2" width="14.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.77734375" style="1" customWidth="1"/>
     <col min="4" max="4" width="40.77734375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.77734375" style="1" customWidth="1"/>
@@ -641,57 +696,113 @@
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="A5" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46227</v>
+      </c>
+      <c r="I5" s="2">
+        <v>46227</v>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="A8" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1379,12 +1490,18 @@
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E39" xr:uid="{1D76DD1E-3D77-457B-B34F-44BCC2B367B7}">
       <formula1>"ต่ำ / Low,ปานกลาง / Medium,สูง / High,วิกฤต / Critical"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F39" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F5 F21:F39" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
       <formula1>"เปิด / Open,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F20" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
+      <formula1>"เปิด / รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F12" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
+      <formula1>"Wait/ รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1393,6 +1510,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -1645,15 +1771,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1668,13 +1785,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{44F13FE1-B81D-4425-A305-6F7F2D16DFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8B379D7-100A-41E9-8B50-E94C6C693C56}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD5B063-C227-4A0F-8154-A968E17D40D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -110,9 +132,6 @@
     <t>ต่ำ / Low</t>
   </si>
   <si>
-    <t>เปิด / รอ</t>
-  </si>
-  <si>
     <t>บริษัท เคบีเอส ซีสเต็ม จํากัด</t>
   </si>
   <si>
@@ -132,6 +151,45 @@
   </si>
   <si>
     <t>เริ่มงานได้ 3 สิงหา</t>
+  </si>
+  <si>
+    <t>Wait/ รอ</t>
+  </si>
+  <si>
+    <t>บริษัท อาร์ทอพ แอร์ ซัพพลาย จำกัด</t>
+  </si>
+  <si>
+    <t>นายคธาชัย จันทร์ศรี</t>
+  </si>
+  <si>
+    <t>หมู่บ้านมัณฑนา</t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง ปลายเดือน 7</t>
+  </si>
+  <si>
+    <t>บริษัทเอ.เอ็น.เอ็นจิเนียริ่งจํากัด</t>
+  </si>
+  <si>
+    <t>บ้านคุณปุกกี้</t>
+  </si>
+  <si>
+    <t>เริ่มงานได้เดือน 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">บ้านบางบอน5ซอย7 </t>
+  </si>
+  <si>
+    <t>เดือน 8 ติดตามสถานะ โปรเจค</t>
+  </si>
+  <si>
+    <t>Main Con กำลังแก้แนวท่อไฟ</t>
+  </si>
+  <si>
+    <t>คุณทวีชัย สมุทรปราการ</t>
+  </si>
+  <si>
+    <t>รองานโครงสร้าง / Site Meeting 8/04/2026</t>
   </si>
 </sst>
 </file>
@@ -274,6 +332,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -602,10 +724,11 @@
     <col min="4" max="4" width="40.77734375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="25.77734375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="20.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.77734375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
@@ -695,7 +818,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="2">
         <v>46226</v>
       </c>
@@ -724,7 +847,9 @@
         <v>46227</v>
       </c>
       <c r="J5" s="4"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="7"/>
     </row>
@@ -745,15 +870,15 @@
         <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -764,23 +889,25 @@
         <v>46226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -791,35 +918,53 @@
         <v>46226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="2"/>
+      <c r="D9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="2">
+        <v>46233</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="4"/>
       <c r="K9" s="3"/>
@@ -827,14 +972,26 @@
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="D10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>46264</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
       <c r="K10" s="3"/>
@@ -842,14 +999,28 @@
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="A11" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
+      <c r="D11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46249</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
       <c r="K11" s="3"/>
@@ -857,13 +1028,25 @@
       <c r="M11" s="7"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="A12" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="D12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
@@ -1510,15 +1693,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -1771,6 +1945,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1785,14 +1968,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1811,6 +1986,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
   <ds:schemaRefs>

--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD5B063-C227-4A0F-8154-A968E17D40D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292D2A6E-DC0D-4DB6-8E62-8ACE19513C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -165,9 +165,6 @@
     <t>หมู่บ้านมัณฑนา</t>
   </si>
   <si>
-    <t>รองานโครงสร้าง ปลายเดือน 7</t>
-  </si>
-  <si>
     <t>บริษัทเอ.เอ็น.เอ็นจิเนียริ่งจํากัด</t>
   </si>
   <si>
@@ -190,6 +187,18 @@
   </si>
   <si>
     <t>รองานโครงสร้าง / Site Meeting 8/04/2026</t>
+  </si>
+  <si>
+    <t>Sukhumvit 77 Prawet Residence</t>
+  </si>
+  <si>
+    <t>รอส่งมอบงาน</t>
+  </si>
+  <si>
+    <t>ปานกลาง / Medium</t>
+  </si>
+  <si>
+    <t>กำลังขึ้นส่วนของหลังคาขั้น 2  ยังไม่สามารถเข้าทำงานได้</t>
   </si>
 </sst>
 </file>
@@ -841,7 +850,7 @@
         <v>18</v>
       </c>
       <c r="H5" s="2">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="I5" s="2">
         <v>46227</v>
@@ -936,7 +945,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -951,7 +960,7 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>22</v>
@@ -960,7 +969,7 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2">
         <v>46233</v>
@@ -976,11 +985,11 @@
         <v>46226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>22</v>
@@ -1003,11 +1012,11 @@
         <v>46226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>22</v>
@@ -1016,7 +1025,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2">
         <v>46249</v>
@@ -1032,11 +1041,11 @@
         <v>46226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>22</v>
@@ -1055,14 +1064,28 @@
       <c r="M12" s="7"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="2"/>
+      <c r="D13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46239</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
       <c r="K13" s="3"/>
@@ -1680,10 +1703,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F5 F21:F39" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
       <formula1>"เปิด / Open,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F20" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F20" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
       <formula1>"เปิด / รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F12" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F13" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
       <formula1>"Wait/ รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1946,15 +1969,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
@@ -1965,6 +1979,15 @@
     <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1987,14 +2010,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2003,4 +2018,12 @@
     <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292D2A6E-DC0D-4DB6-8E62-8ACE19513C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -997,7 +997,9 @@
       <c r="F10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="H10" s="2">
         <v>46264</v>
       </c>

--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPVICTUS\OneDrive - Coral Life\Coral Life - BA - Solution Design 1\1_Non-Project\7_Engineer\IAQ Solution\0_ERV Management\2_Construction Management\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1718,6 +1718,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -1970,29 +1992,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2009,23 +2028,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAB7A5CD-E37D-4691-9681-CCCF898CE336}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Defect Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Project Problems" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,9 +81,6 @@
     <t>หมายเหตุ / Remarks</t>
   </si>
   <si>
-    <t xml:space="preserve">DEFECT REPORT </t>
-  </si>
-  <si>
     <t>Project</t>
   </si>
   <si>
@@ -199,6 +196,9 @@
   </si>
   <si>
     <t>กำลังขึ้นส่วนของหลังคาขั้น 2  ยังไม่สามารถเข้าทำงานได้</t>
+  </si>
+  <si>
+    <t>PROJECT PROBLEMS</t>
   </si>
 </sst>
 </file>
@@ -743,7 +743,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A1" s="9" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
@@ -793,22 +793,22 @@
         <v>4</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="K3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="M3" s="7"/>
     </row>
@@ -832,22 +832,22 @@
         <v>46226</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="H5" s="2">
         <v>46226</v>
@@ -867,27 +867,27 @@
         <v>46226</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -898,25 +898,25 @@
         <v>46226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -927,25 +927,25 @@
         <v>46226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -956,20 +956,20 @@
         <v>46226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2">
         <v>46233</v>
@@ -985,20 +985,20 @@
         <v>46226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2">
         <v>46264</v>
@@ -1014,20 +1014,20 @@
         <v>46226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2">
         <v>46249</v>
@@ -1043,20 +1043,20 @@
         <v>46226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1070,20 +1070,20 @@
         <v>46226</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2">
         <v>46239</v>
@@ -1718,28 +1718,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -1992,10 +1970,43 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2012,20 +2023,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAB7A5CD-E37D-4691-9681-CCCF898CE336}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2908BE3F-02A2-44F7-B052-5E6E78934DA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -120,9 +120,6 @@
     <t>S’rin House</t>
   </si>
   <si>
-    <t>ห้องกล๊ออฟ</t>
-  </si>
-  <si>
     <t>รองานโครงสร้าง</t>
   </si>
   <si>
@@ -199,6 +196,21 @@
   </si>
   <si>
     <t>PROJECT PROBLEMS</t>
+  </si>
+  <si>
+    <t>ห้องกอล์ฟ</t>
+  </si>
+  <si>
+    <t>บ้านคุณพงษ์ เอกมัย 28</t>
+  </si>
+  <si>
+    <t>แก้ไขแนวท่อหลัง Coring</t>
+  </si>
+  <si>
+    <t>รออัพเดทPrpgres จากหน้างาน</t>
+  </si>
+  <si>
+    <t>บริษัท อีโค่คูล</t>
   </si>
 </sst>
 </file>
@@ -328,7 +340,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -408,7 +420,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -743,7 +755,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A1" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -870,24 +882,24 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -898,25 +910,25 @@
         <v>46226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -927,25 +939,25 @@
         <v>46226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -956,20 +968,20 @@
         <v>46226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="2">
         <v>46233</v>
@@ -985,17 +997,17 @@
         <v>46226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>17</v>
@@ -1014,20 +1026,20 @@
         <v>46226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="2">
         <v>46249</v>
@@ -1043,20 +1055,20 @@
         <v>46226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1070,20 +1082,20 @@
         <v>46226</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2">
         <v>46239</v>
@@ -1095,16 +1107,34 @@
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="2">
+        <v>46224</v>
+      </c>
+      <c r="I14" s="2">
+        <v>46227</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="7"/>

--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2908BE3F-02A2-44F7-B052-5E6E78934DA1}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE610DF3-82A2-4445-869B-EFFD99E7E9BB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -51,17 +51,27 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="1">
+  <valueMetadata count="2">
     <bk>
       <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="55">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -114,9 +124,6 @@
     <t>กำลังแก้ / In Progress</t>
   </si>
   <si>
-    <t>3T</t>
-  </si>
-  <si>
     <t>S’rin House</t>
   </si>
   <si>
@@ -207,10 +214,28 @@
     <t>แก้ไขแนวท่อหลัง Coring</t>
   </si>
   <si>
-    <t>รออัพเดทPrpgres จากหน้างาน</t>
-  </si>
-  <si>
-    <t>บริษัท อีโค่คูล</t>
+    <t>บริษัท อีโค่คูล ไคลเมท เทคโนโลยี จำกัด</t>
+  </si>
+  <si>
+    <t>รออัพเดท Prpgres จากหน้างาน</t>
+  </si>
+  <si>
+    <t>บ้านคุณ ศรุต บางประอิน</t>
+  </si>
+  <si>
+    <t>ชั้น1-2 / ห้องไฟฟ้า</t>
+  </si>
+  <si>
+    <t>รอบิ้วอินเพื่อติดตั้งจอ LCD /  รอฝ้าเพื่อติดกริว</t>
+  </si>
+  <si>
+    <t>บริษัท สาม.ที เอ็นจิเนียริ่ง จำกัด</t>
+  </si>
+  <si>
+    <t>The Grand Pinklao Residence</t>
+  </si>
+  <si>
+    <t>เข้าติดตั้ง/นัดส่งงานลูกค้า 100% วันจันทร์ 27/07/2026</t>
   </si>
 </sst>
 </file>
@@ -315,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -337,6 +362,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -396,9 +424,13 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <rv s="0">
     <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -416,6 +448,7 @@
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
 </richValueRels>
 </file>
 
@@ -745,7 +778,7 @@
     <col min="4" max="4" width="40.77734375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" style="1" customWidth="1"/>
     <col min="8" max="9" width="14.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="25.77734375" style="1" customWidth="1"/>
     <col min="11" max="11" width="34.6640625" style="1" customWidth="1"/>
@@ -755,7 +788,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A1" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -859,7 +892,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H5" s="2">
         <v>46226</v>
@@ -879,27 +912,27 @@
         <v>46226</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -910,25 +943,25 @@
         <v>46226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -939,25 +972,25 @@
         <v>46226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -968,20 +1001,20 @@
         <v>46226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2">
         <v>46233</v>
@@ -997,20 +1030,20 @@
         <v>46226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H10" s="2">
         <v>46264</v>
@@ -1026,20 +1059,20 @@
         <v>46226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2">
         <v>46249</v>
@@ -1055,20 +1088,20 @@
         <v>46226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1082,20 +1115,20 @@
         <v>46226</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13" s="2">
         <v>46239</v>
@@ -1106,16 +1139,16 @@
       <c r="L13" s="3"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2">
         <v>46226</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>15</v>
@@ -1124,7 +1157,7 @@
         <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H14" s="2">
         <v>46224</v>
@@ -1135,19 +1168,37 @@
       <c r="J14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="10" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="7"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="2"/>
+      <c r="A15" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="2">
+        <v>46265</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="4"/>
       <c r="K15" s="3"/>
@@ -1155,15 +1206,31 @@
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2">
+        <v>46226</v>
+      </c>
+      <c r="I16" s="2">
+        <v>46230</v>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1728,17 +1795,17 @@
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E39" xr:uid="{1D76DD1E-3D77-457B-B34F-44BCC2B367B7}">
       <formula1>"ต่ำ / Low,ปานกลาง / Medium,สูง / High,วิกฤต / Critical"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F5 F21:F39" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
       <formula1>"เปิด / Open,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F20" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14 F16:F20" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
       <formula1>"เปิด / รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F13" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F13 F15" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
       <formula1>"Wait/ รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE610DF3-82A2-4445-869B-EFFD99E7E9BB}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC2EBBB-5B43-4231-8BE0-99A2E94EF9C8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -58,20 +58,30 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -236,6 +246,18 @@
   </si>
   <si>
     <t>เข้าติดตั้ง/นัดส่งงานลูกค้า 100% วันจันทร์ 27/07/2026</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">จอยังใส่ไม่ได้ 2 จุด </t>
+  </si>
+  <si>
+    <t>รอช่างบิ้วอิน เข้าติดจอกับผนังให้</t>
+  </si>
+  <si>
+    <t>อาคาร A</t>
   </si>
 </sst>
 </file>
@@ -360,11 +382,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -381,6 +403,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1341121</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>302</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2358393</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1356360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAABC83B-E19B-3E0A-9CCE-2E0306F90835}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15727681" y="3086402"/>
+          <a:ext cx="1017272" cy="1356058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,13 +495,17 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
     <v>0</v>
     <v>5</v>
   </rv>
   <rv s="0">
     <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -449,6 +524,7 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -769,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA9E12A-0D38-4050-91CC-6CC920F9BA63}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="14.77734375" style="1" customWidth="1"/>
@@ -787,19 +863,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
       <c r="L1" s="5"/>
       <c r="M1" s="7"/>
     </row>
@@ -907,34 +983,38 @@
       <c r="L5" s="3"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="2">
         <v>46226</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="H6" s="2">
+        <v>46237</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="K6" s="3" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="7"/>
     </row>
@@ -943,11 +1023,13 @@
         <v>46226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="D7" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>19</v>
@@ -956,12 +1038,12 @@
         <v>27</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -972,11 +1054,11 @@
         <v>46226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>19</v>
@@ -985,12 +1067,12 @@
         <v>27</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1001,11 +1083,11 @@
         <v>46226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>19</v>
@@ -1014,13 +1096,13 @@
         <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="2">
-        <v>46233</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="7"/>
@@ -1030,11 +1112,11 @@
         <v>46226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>19</v>
@@ -1043,10 +1125,10 @@
         <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H10" s="2">
-        <v>46264</v>
+        <v>46233</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
@@ -1059,11 +1141,11 @@
         <v>46226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>19</v>
@@ -1072,10 +1154,10 @@
         <v>27</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H11" s="2">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
@@ -1088,11 +1170,11 @@
         <v>46226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>19</v>
@@ -1101,9 +1183,11 @@
         <v>27</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="H12" s="2">
+        <v>46249</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
       <c r="K12" s="3"/>
@@ -1115,93 +1199,89 @@
         <v>46226</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="2">
-        <v>46239</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" s="2">
         <v>46226</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H14" s="2">
-        <v>46224</v>
-      </c>
-      <c r="I14" s="2">
-        <v>46227</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="10" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
+        <v>46239</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2">
         <v>46226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="2">
-        <v>46265</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="3"/>
+        <v>46224</v>
+      </c>
+      <c r="I15" s="2">
+        <v>46227</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="9" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="7"/>
     </row>
@@ -1210,42 +1290,58 @@
         <v>46226</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="D16" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2">
-        <v>46226</v>
-      </c>
-      <c r="I16" s="2">
-        <v>46230</v>
-      </c>
+        <v>46265</v>
+      </c>
+      <c r="I16" s="2"/>
       <c r="J16" s="4"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="A17" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2">
+        <v>46226</v>
+      </c>
+      <c r="I17" s="2">
+        <v>46230</v>
+      </c>
       <c r="J17" s="4"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -1582,18 +1678,18 @@
       <c r="M39" s="7"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
       <c r="M40" s="7"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.5">
@@ -1791,30 +1887,68 @@
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E39" xr:uid="{1D76DD1E-3D77-457B-B34F-44BCC2B367B7}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E40" xr:uid="{1D76DD1E-3D77-457B-B34F-44BCC2B367B7}">
       <formula1>"ต่ำ / Low,ปานกลาง / Medium,สูง / High,วิกฤต / Critical"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F5 F21:F39" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F40 F4:F6" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
       <formula1>"เปิด / Open,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14 F16:F20" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15 F17:F21" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
       <formula1>"เปิด / รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F13 F15" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F14 F16" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
       <formula1>"Wait/ รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
+    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008ED2D49705E83042817996DE5E733B41" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ba94834c452bdfc5c8776e4d6f86dfb3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xmlns:ns3="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff4bedaaabc80ab55b5467b16ce003eb" ns2:_="" ns3:_="">
     <xsd:import namespace="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
@@ -2067,29 +2201,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Complete xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2d1b07a1-7849-4740-a4b1-3343cd5aadb6" xsi:nil="true"/>
-    <DateStart xmlns="d1b9d38e-82c4-40dd-a627-c28ab9108e1c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
+    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23449C61-D5BA-44B1-A472-FB4C9EEC61EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2106,23 +2237,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B76825-6942-4800-BFAC-87DF8A7A9F61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1b9d38e-82c4-40dd-a627-c28ab9108e1c"/>
-    <ds:schemaRef ds:uri="2d1b07a1-7849-4740-a4b1-3343cd5aadb6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF18A786-B973-49B0-99B2-5E7AF5814A3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC2EBBB-5B43-4231-8BE0-99A2E94EF9C8}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F1F971C-1595-4A75-99FF-2F71308B0B14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -43,7 +43,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="4">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -65,8 +65,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="4">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -76,12 +83,15 @@
     <bk>
       <rc t="1" v="2"/>
     </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="61">
   <si>
     <t>วันที่ / Date</t>
   </si>
@@ -258,6 +268,12 @@
   </si>
   <si>
     <t>อาคาร A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ชั้น1-2 </t>
+  </si>
+  <si>
+    <t>จอยังติดตั้งจอไม่ได้ / ยังไม่มี Power 220 V.มาจ่ายที่ Junction Box</t>
   </si>
 </sst>
 </file>
@@ -451,6 +467,94 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>754561</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1650948</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1358354</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1FC3686-9FDC-84B0-D0D5-4147C612D9B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15141121" y="4450080"/>
+          <a:ext cx="896387" cy="1358354"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1524000</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2362200</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>15238</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C81182D5-1837-8C68-13B2-1E5C4623B40D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15910560" y="4465320"/>
+          <a:ext cx="838200" cy="1363978"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -495,7 +599,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -506,6 +610,10 @@
   </rv>
   <rv s="0">
     <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -525,6 +633,7 @@
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
 </richValueRels>
 </file>
 
@@ -845,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA9E12A-0D38-4050-91CC-6CC920F9BA63}">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="14.77734375" style="1" customWidth="1"/>
@@ -1018,7 +1127,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="7"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="2">
         <v>46226</v>
       </c>
@@ -1026,26 +1135,30 @@
         <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46237</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="7"/>
     </row>
@@ -1054,11 +1167,13 @@
         <v>46226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="D8" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>19</v>
@@ -1067,12 +1182,12 @@
         <v>27</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1083,11 +1198,11 @@
         <v>46226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>19</v>
@@ -1096,12 +1211,12 @@
         <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="4" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1112,11 +1227,11 @@
         <v>46226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>19</v>
@@ -1125,13 +1240,13 @@
         <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="2">
-        <v>46233</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="7"/>
@@ -1141,11 +1256,11 @@
         <v>46226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>19</v>
@@ -1154,10 +1269,10 @@
         <v>27</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2">
-        <v>46264</v>
+        <v>46233</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
@@ -1170,11 +1285,11 @@
         <v>46226</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>19</v>
@@ -1183,10 +1298,10 @@
         <v>27</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
@@ -1199,11 +1314,11 @@
         <v>46226</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>19</v>
@@ -1212,9 +1327,11 @@
         <v>27</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="H13" s="2">
+        <v>46249</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
       <c r="K13" s="3"/>
@@ -1226,93 +1343,89 @@
         <v>46226</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="2">
-        <v>46239</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="4"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" s="2">
         <v>46226</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H15" s="2">
-        <v>46224</v>
-      </c>
-      <c r="I15" s="2">
-        <v>46227</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="9" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
+        <v>46239</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:13" ht="107.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2">
         <v>46226</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C16" s="3"/>
       <c r="D16" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>47</v>
       </c>
       <c r="H16" s="2">
-        <v>46265</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="3"/>
+        <v>46224</v>
+      </c>
+      <c r="I16" s="2">
+        <v>46227</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="9" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="7"/>
     </row>
@@ -1321,42 +1434,58 @@
         <v>46226</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="D17" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="H17" s="2">
-        <v>46226</v>
-      </c>
-      <c r="I17" s="2">
-        <v>46230</v>
-      </c>
+        <v>46265</v>
+      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="4"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="A18" s="2">
+        <v>46226</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="D18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2">
+        <v>46226</v>
+      </c>
+      <c r="I18" s="2">
+        <v>46230</v>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -1693,18 +1822,18 @@
       <c r="M40" s="7"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="7"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.5">
@@ -1902,21 +2031,36 @@
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
     </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E40" xr:uid="{1D76DD1E-3D77-457B-B34F-44BCC2B367B7}">
+  <dataValidations disablePrompts="1" count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E41" xr:uid="{1D76DD1E-3D77-457B-B34F-44BCC2B367B7}">
       <formula1>"ต่ำ / Low,ปานกลาง / Medium,สูง / High,วิกฤต / Critical"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22:F40 F4:F6" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F23:F41 F4:F6" xr:uid="{9142C414-FBEE-4106-981C-B95747E09F3E}">
       <formula1>"เปิด / Open,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15 F17:F21" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16 F18:F22" xr:uid="{CDB5D18A-3777-490D-9FBC-6359E5CBE300}">
       <formula1>"เปิด / รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F14 F16" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F15 F17" xr:uid="{60ECFCFC-3AD4-4842-BAB6-A7EB051C8426}">
       <formula1>"Wait/ รอ,กำลังแก้ / In Progress,แก้เสร็จ / Fixed,ปิด / Closed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Defect_Report.xlsx
+++ b/Defect_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corallife806.sharepoint.com/sites/CoralLife2/Document Sharing/BA - Solution Design/1_Non-Project/7_Engineer/IAQ Solution/0_ERV Management/2_Construction Management/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F1F971C-1595-4A75-99FF-2F71308B0B14}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{5F02B2AC-815D-42F3-A0FD-6095082C3EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EAB8D68-D5B9-4C57-B031-02805A86A65D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{04FC0AC7-FBBE-4BBC-BC06-125512EACFB3}"/>
   </bookViews>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -403,6 +403,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,15 +473,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>754561</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>769801</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1356360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1650948</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1358354</xdr:rowOff>
+      <xdr:colOff>1666188</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -501,8 +504,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15141121" y="4450080"/>
-          <a:ext cx="896387" cy="1358354"/>
+          <a:off x="15156361" y="4442460"/>
+          <a:ext cx="896387" cy="1379220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -514,15 +517,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1524000</xdr:colOff>
+      <xdr:colOff>1539240</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>2362200</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>15238</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -545,8 +548,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15910560" y="4465320"/>
-          <a:ext cx="838200" cy="1363978"/>
+          <a:off x="15925800" y="4450080"/>
+          <a:ext cx="838200" cy="1371600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1121,7 +1124,7 @@
       <c r="J6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="3" t="e" vm="2">
+      <c r="K6" s="11" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="L6" s="3"/>
